--- a/Requirements/Babysteps_Implemented_Requirements_Gap_Audit_v45.xlsx
+++ b/Requirements/Babysteps_Implemented_Requirements_Gap_Audit_v45.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sridhar\Projects\BabyStepsIndia\Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE387FF0-8AF2-45B7-A51D-75CD6F422D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B95AE4-C3DA-4037-BC0D-853A280FEC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="21336" windowHeight="11376" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="921">
   <si>
     <t>Babysteps v45 — Implemented Requirements Gap Audit</t>
   </si>
@@ -413,9 +413,6 @@
     <t>https://github.com/SridharVoleti/babystepsindia/blob/master/README.md</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>GAP-002</t>
   </si>
   <si>
@@ -2685,6 +2682,123 @@
   </si>
   <si>
     <t>Deferred  -  platform: requires activating Supabase Auth in production (current runtime is local SQLite + built-in session auth by design, see README).</t>
+  </si>
+  <si>
+    <t>Deferred - platform: requires configuring production email delivery (Supabase/custom SMTP callbacks); same root cause as GAP-001/004.</t>
+  </si>
+  <si>
+    <t>Resolved - IA-004 WebAuthn built (src/lib/webauthn/service.ts); real passkey registration/authentication now backs the learner-lock trust boundary, closing the dependency.</t>
+  </si>
+  <si>
+    <t>Resolved - added cross-requirement integration tests (tests/gap-018-lp002-session-integration.test.ts) covering a date-of-birth change against weekly session-slot usage and analytics age-band attribution across the full session lifecycle.</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001 browser runtime SDK built (src/lib/session-runtime-sdk/): real IndexedDB-backed runtime with Web Locks + BroadcastChannel single-owner-tab coordination.</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001 browser runtime SDK: real IndexedDB persistence via createRuntime/recordMeaningfulChange, only writing at meaningful boundaries.</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001 browser runtime SDK: checkpointIfDue implements the five-minute change-gated safety checkpoint with deterministic clock tests.</t>
+  </si>
+  <si>
+    <t>Resolved - IA-004 WebAuthn cryptographically unlocks learner mode via activateLearnerMode's one-time verificationReceiptId, consumed only after a real passkey assertion verifies (recordTrustedPasskeyVerification).</t>
+  </si>
+  <si>
+    <t>Deferred - platform: requires the full BI/EN billing lifecycle (product/bundle catalog, checkout, payment gateway) that does not exist in this repo; same root cause as GAP-084/086/088/094/096/097/099.</t>
+  </si>
+  <si>
+    <t>Resolved - AU-004 Ed25519 managed machine identity; AN-001 scheduler/contributor platform-service principals now sign with EdDSA, verified against a stored public key, no shared secret.</t>
+  </si>
+  <si>
+    <t>Resolved - PR-001 progress schema registry (src/lib/progress-schema-registry/service.ts) gate wired into AR-002's approveProduction via assertReleaseSchemaCompatibility; a release with no forward+rollback migration path from an in-use schema version cannot promote.</t>
+  </si>
+  <si>
+    <t>Resolved - AU-004 Ed25519; app-service client assertions now use a per-principal Ed25519 key pair, no HS256 shared secret.</t>
+  </si>
+  <si>
+    <t>Resolved - AU-004; APP_SERVICE_SECRETS/PLATFORM_SERVICE_SECRETS env-var secret maps removed entirely from the codebase.</t>
+  </si>
+  <si>
+    <t>Resolved - AU-004; LA-002 fresh app assertion now verified via the principal's stored Ed25519 public key.</t>
+  </si>
+  <si>
+    <t>Resolved - PR-001 schema registry: deterministic declarative (rename/default/drop) migrators walked step-by-step, plus the AR-002 forward/rollback compatibility gate.</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001's prepareResume implements the signed/bound (HMAC over a device-local key that never leaves IndexedDB) pending capsule with hard-expiry and server-progress-version checks, one-time recovery.</t>
+  </si>
+  <si>
+    <t>Resolved - PR-003 standard app-owned progress summary contract (current level, efficiency stars, milestone, next destination) added to saveCheckpoint/completeLesson, validated and persisted on learner_app_progress.progress_summary_json.</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001's checkpointIfDue implements the five-minute change-gated checkpoint; ordinary interaction (clicks/navigation) never reaches a DB write, proven by a test spanning a simulated 45-minute session.</t>
+  </si>
+  <si>
+    <t>Resolved - same AR-002 promotion gate as GAP-037 (assertReleaseSchemaCompatibility blocks promotion without a safe schema migration path).</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001's prepareResume/checkpointIfDue give LA-004 completion a real local pending-capsule flush/retry and original-device-bounded recovery path.</t>
+  </si>
+  <si>
+    <t>Resolved - PR-003 summary is surfaced again at session finalization (finalProgressSummary in the finalizeLearnerSession response).</t>
+  </si>
+  <si>
+    <t>Resolved - AU-004; AU-001's app-service context now derives only from a verified Ed25519-signed managed principal.</t>
+  </si>
+  <si>
+    <t>Resolved - IA-004: full WebAuthn registration/authentication implementation (@simplewebauthn/server) with real ECDSA ceremonies, tested via a from-scratch virtual authenticator, not mocks.</t>
+  </si>
+  <si>
+    <t>Resolved - activateLearnerMode already took a verificationReceiptId (not a boolean); IA-004 now supplies the real verifier that produces that receipt only after genuine WebAuthn verification.</t>
+  </si>
+  <si>
+    <t>Resolved - IA-004: 5-minute single-use hashed (never raw) WebAuthn challenges in webauthn_challenges, consumed exactly once.</t>
+  </si>
+  <si>
+    <t>Resolved - IA-004: learner_passkey_credentials registry with label, active/revoked state, sign-counter clone detection, and reauth-protected revocation that also tears down any active learner-mode context bound to the credential.</t>
+  </si>
+  <si>
+    <t>Resolved - IA-004: locked-learner enrollment/unlock UI (src/components/learner-mode/passkey-unlock.tsx) with explicit browserSupportsWebAuthn() feature detection and no password/PIN fallback.</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001 browser runtime SDK: real IndexedDB implementation (src/lib/session-runtime-sdk/idb.ts) in the shared learning-app SDK.</t>
+  </si>
+  <si>
+    <t>Resolved - session envelope switched from HS256 to EdDSA specifically so the browser SDK's createRuntime can verify it with only the Ed25519 public key, before any local runtime is created.</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001's claimOwnerTab: Web Locks single-owner-tab lease plus BroadcastChannel coordination, tested against a mocked LockManager for real acquire/contend/release semantics.</t>
+  </si>
+  <si>
+    <t>Resolved - same pending-capsule mechanism as GAP-055 (signing/binding, hard-expiry check, server-version comparison, one-time recovery).</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001 migrations.ts: versioned local runtime migrators with fail-closed behavior on an unrecognized future version, exercised end-to-end.</t>
+  </si>
+  <si>
+    <t>Resolved - test proves zero network/platform-DB calls occur across a simulated 45-minute session absent a due+dirty checkpoint (only meaningful changes ever produce a sync call).</t>
+  </si>
+  <si>
+    <t>Resolved - SC-001 browser runtime SDK provides the real SDK-boot/IndexedDB-initialization half of the handshake; the app backend's own usable-launch callback into the already-real POST usable-launch route is the out-of-repo half, same boundary as GAP-052.</t>
+  </si>
+  <si>
+    <t>Resolved - AU-004; SC-003 usable-launch dual proof now uses Ed25519 app-service assertions.</t>
+  </si>
+  <si>
+    <t>Resolved - PR-001's migrateLearnerProgressToReleaseSchema wired into confirmUsableLaunch, running before funding consumption and blocking (leaving funding untouched) if no migration path exists.</t>
+  </si>
+  <si>
+    <t>Deferred - platform: requires BI/EN-003 lifecycle event producers (grace/cancellation) that do not exist; same root cause as GAP-097/103/104.</t>
+  </si>
+  <si>
+    <t>Resolved - AU-004; the apply-paid-cycle/evaluate-access internal routes already required requireInternalService, now backed by verified Ed25519 managed principals instead of an HS256 shared-secret scheme.</t>
+  </si>
+  <si>
+    <t>Resolved - evaluateAccessForLauncher (src/lib/entitlement-access/launcher-cache.ts): a bounded, read-only cache for launcher/home-screen display only, expiring at the sooner of a 60s TTL or the decision's own nearest entitlement/app boundary; never consulted by Start/exchange/usable-launch/resume.</t>
+  </si>
+  <si>
+    <t>Deferred - platform: requires EN-003 lifecycle overlays (grace/cancel) driven by a BI producer that does not exist; same root cause as GAP-093/097/103/104.</t>
   </si>
 </sst>
 </file>
@@ -2765,9 +2879,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFF2CC"/>
@@ -2794,6 +2905,9 @@
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3298,7 +3412,7 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Code Evidence URL"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Requirements Source"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Status"/>
-    <tableColumn id="12" xr3:uid="{DCDEB6CB-FAAC-4736-ADD7-1007E1B5A87B}" name="Resolution Notes" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{DCDEB6CB-FAAC-4736-ADD7-1007E1B5A87B}" name="Resolution Notes" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15726,7 +15840,7 @@
         <v>117</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -15775,10 +15889,10 @@
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -15797,7 +15911,7 @@
     </row>
     <row r="3" spans="1:26" ht="41.4">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>28</v>
@@ -15806,30 +15920,32 @@
         <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L3" s="1"/>
+        <v>832</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>882</v>
+      </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -15847,7 +15963,7 @@
     </row>
     <row r="4" spans="1:26" ht="27.6">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>28</v>
@@ -15856,19 +15972,19 @@
         <v>50</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>124</v>
@@ -15877,10 +15993,10 @@
         <v>15</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -15899,7 +16015,7 @@
     </row>
     <row r="5" spans="1:26" ht="27.6">
       <c r="A5" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>28</v>
@@ -15908,19 +16024,19 @@
         <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>124</v>
@@ -15929,10 +16045,10 @@
         <v>15</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -15951,7 +16067,7 @@
     </row>
     <row r="6" spans="1:26" ht="27.6">
       <c r="A6" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>32</v>
@@ -15963,16 +16079,16 @@
         <v>119</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>124</v>
@@ -15981,10 +16097,10 @@
         <v>15</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -16003,28 +16119,28 @@
     </row>
     <row r="7" spans="1:26" ht="41.4">
       <c r="A7" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>124</v>
@@ -16033,10 +16149,10 @@
         <v>15</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -16055,7 +16171,7 @@
     </row>
     <row r="8" spans="1:26" ht="27.6">
       <c r="A8" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>32</v>
@@ -16064,19 +16180,19 @@
         <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>124</v>
@@ -16085,10 +16201,10 @@
         <v>15</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -16107,40 +16223,40 @@
     </row>
     <row r="9" spans="1:26" ht="41.4">
       <c r="A9" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -16159,7 +16275,7 @@
     </row>
     <row r="10" spans="1:26" ht="27.6">
       <c r="A10" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>34</v>
@@ -16168,31 +16284,31 @@
         <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -16211,7 +16327,7 @@
     </row>
     <row r="11" spans="1:26" ht="55.2">
       <c r="A11" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>34</v>
@@ -16220,31 +16336,31 @@
         <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -16263,7 +16379,7 @@
     </row>
     <row r="12" spans="1:26" ht="27.6">
       <c r="A12" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>34</v>
@@ -16272,31 +16388,31 @@
         <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="I12" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -16315,7 +16431,7 @@
     </row>
     <row r="13" spans="1:26" ht="27.6">
       <c r="A13" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>34</v>
@@ -16324,31 +16440,31 @@
         <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -16367,7 +16483,7 @@
     </row>
     <row r="14" spans="1:26" ht="27.6">
       <c r="A14" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>36</v>
@@ -16376,31 +16492,31 @@
         <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -16419,7 +16535,7 @@
     </row>
     <row r="15" spans="1:26" ht="41.4">
       <c r="A15" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>36</v>
@@ -16428,30 +16544,32 @@
         <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L15" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>883</v>
+      </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -16469,28 +16587,28 @@
     </row>
     <row r="16" spans="1:26" ht="41.4">
       <c r="A16" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>124</v>
@@ -16499,10 +16617,10 @@
         <v>15</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -16521,7 +16639,7 @@
     </row>
     <row r="17" spans="1:26" ht="27.6">
       <c r="A17" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>38</v>
@@ -16530,31 +16648,31 @@
         <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -16573,7 +16691,7 @@
     </row>
     <row r="18" spans="1:26" ht="41.4">
       <c r="A18" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>38</v>
@@ -16582,31 +16700,31 @@
         <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -16625,39 +16743,41 @@
     </row>
     <row r="19" spans="1:26" ht="41.4">
       <c r="A19" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L19" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>884</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -16675,40 +16795,40 @@
     </row>
     <row r="20" spans="1:26" ht="27.6">
       <c r="A20" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -16727,7 +16847,7 @@
     </row>
     <row r="21" spans="1:26" ht="27.6">
       <c r="A21" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>40</v>
@@ -16736,19 +16856,19 @@
         <v>31</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>124</v>
@@ -16757,9 +16877,11 @@
         <v>15</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L21" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>885</v>
+      </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -16777,7 +16899,7 @@
     </row>
     <row r="22" spans="1:26" ht="27.6">
       <c r="A22" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>40</v>
@@ -16786,19 +16908,19 @@
         <v>31</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>124</v>
@@ -16807,9 +16929,11 @@
         <v>15</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L22" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>886</v>
+      </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -16827,7 +16951,7 @@
     </row>
     <row r="23" spans="1:26" ht="27.6">
       <c r="A23" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>40</v>
@@ -16836,19 +16960,19 @@
         <v>31</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>124</v>
@@ -16857,9 +16981,11 @@
         <v>15</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L23" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>887</v>
+      </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -16877,7 +17003,7 @@
     </row>
     <row r="24" spans="1:26" ht="27.6">
       <c r="A24" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>40</v>
@@ -16886,30 +17012,32 @@
         <v>31</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="I24" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L24" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>888</v>
+      </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -16927,7 +17055,7 @@
     </row>
     <row r="25" spans="1:26" ht="27.6">
       <c r="A25" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>40</v>
@@ -16936,19 +17064,19 @@
         <v>50</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>124</v>
@@ -16957,10 +17085,10 @@
         <v>15</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -16979,7 +17107,7 @@
     </row>
     <row r="26" spans="1:26" ht="27.6">
       <c r="A26" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>40</v>
@@ -16988,30 +17116,32 @@
         <v>50</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L26" s="1"/>
+        <v>832</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>889</v>
+      </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -17029,7 +17159,7 @@
     </row>
     <row r="27" spans="1:26" ht="27.6">
       <c r="A27" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>43</v>
@@ -17038,19 +17168,19 @@
         <v>50</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>124</v>
@@ -17059,10 +17189,10 @@
         <v>15</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -17081,7 +17211,7 @@
     </row>
     <row r="28" spans="1:26" ht="27.6">
       <c r="A28" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>43</v>
@@ -17090,19 +17220,19 @@
         <v>50</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>124</v>
@@ -17111,10 +17241,10 @@
         <v>15</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -17133,28 +17263,28 @@
     </row>
     <row r="29" spans="1:26" ht="41.4">
       <c r="A29" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>124</v>
@@ -17163,10 +17293,10 @@
         <v>15</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -17185,7 +17315,7 @@
     </row>
     <row r="30" spans="1:26" ht="27.6">
       <c r="A30" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>45</v>
@@ -17194,19 +17324,19 @@
         <v>50</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>124</v>
@@ -17215,10 +17345,10 @@
         <v>15</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -17237,7 +17367,7 @@
     </row>
     <row r="31" spans="1:26" ht="27.6">
       <c r="A31" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>45</v>
@@ -17246,30 +17376,32 @@
         <v>50</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="I31" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L31" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>890</v>
+      </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -17287,28 +17419,28 @@
     </row>
     <row r="32" spans="1:26" ht="27.6">
       <c r="A32" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>124</v>
@@ -17317,10 +17449,10 @@
         <v>15</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -17339,7 +17471,7 @@
     </row>
     <row r="33" spans="1:26" ht="27.6">
       <c r="A33" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>47</v>
@@ -17348,19 +17480,19 @@
         <v>31</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>124</v>
@@ -17369,10 +17501,10 @@
         <v>15</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -17391,7 +17523,7 @@
     </row>
     <row r="34" spans="1:26" ht="27.6">
       <c r="A34" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>47</v>
@@ -17400,19 +17532,19 @@
         <v>31</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>124</v>
@@ -17421,10 +17553,10 @@
         <v>15</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -17443,7 +17575,7 @@
     </row>
     <row r="35" spans="1:26" ht="27.6">
       <c r="A35" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>47</v>
@@ -17452,19 +17584,19 @@
         <v>31</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>124</v>
@@ -17473,10 +17605,10 @@
         <v>15</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -17495,7 +17627,7 @@
     </row>
     <row r="36" spans="1:26" ht="27.6">
       <c r="A36" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>47</v>
@@ -17504,19 +17636,19 @@
         <v>31</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="H36" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>124</v>
@@ -17525,10 +17657,10 @@
         <v>15</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -17547,7 +17679,7 @@
     </row>
     <row r="37" spans="1:26" ht="27.6">
       <c r="A37" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>47</v>
@@ -17556,19 +17688,19 @@
         <v>31</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>124</v>
@@ -17577,10 +17709,10 @@
         <v>15</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -17599,7 +17731,7 @@
     </row>
     <row r="38" spans="1:26" ht="27.6">
       <c r="A38" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>47</v>
@@ -17608,19 +17740,19 @@
         <v>31</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>124</v>
@@ -17629,9 +17761,11 @@
         <v>15</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L38" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>891</v>
+      </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -17649,7 +17783,7 @@
     </row>
     <row r="39" spans="1:26" ht="27.6">
       <c r="A39" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>47</v>
@@ -17658,19 +17792,19 @@
         <v>31</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="H39" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>124</v>
@@ -17679,10 +17813,10 @@
         <v>15</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
@@ -17701,7 +17835,7 @@
     </row>
     <row r="40" spans="1:26" ht="27.6">
       <c r="A40" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>47</v>
@@ -17710,19 +17844,19 @@
         <v>31</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>124</v>
@@ -17731,10 +17865,10 @@
         <v>15</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -17753,7 +17887,7 @@
     </row>
     <row r="41" spans="1:26" ht="27.6">
       <c r="A41" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>47</v>
@@ -17762,19 +17896,19 @@
         <v>31</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>124</v>
@@ -17783,10 +17917,10 @@
         <v>15</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
@@ -17805,7 +17939,7 @@
     </row>
     <row r="42" spans="1:26" ht="41.4">
       <c r="A42" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>47</v>
@@ -17814,19 +17948,19 @@
         <v>50</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>124</v>
@@ -17835,10 +17969,10 @@
         <v>15</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
@@ -17857,7 +17991,7 @@
     </row>
     <row r="43" spans="1:26" ht="27.6">
       <c r="A43" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>51</v>
@@ -17866,30 +18000,32 @@
         <v>31</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="I43" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L43" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>892</v>
+      </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -17907,7 +18043,7 @@
     </row>
     <row r="44" spans="1:26" ht="41.4">
       <c r="A44" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>51</v>
@@ -17916,31 +18052,31 @@
         <v>31</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -17959,7 +18095,7 @@
     </row>
     <row r="45" spans="1:26" ht="41.4">
       <c r="A45" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>51</v>
@@ -17968,19 +18104,19 @@
         <v>50</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>124</v>
@@ -17989,10 +18125,10 @@
         <v>15</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
@@ -18011,7 +18147,7 @@
     </row>
     <row r="46" spans="1:26" ht="27.6">
       <c r="A46" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>51</v>
@@ -18020,19 +18156,19 @@
         <v>50</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="G46" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>124</v>
@@ -18041,10 +18177,10 @@
         <v>15</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
@@ -18063,7 +18199,7 @@
     </row>
     <row r="47" spans="1:26" ht="27.6">
       <c r="A47" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>51</v>
@@ -18072,31 +18208,31 @@
         <v>50</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="I47" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
@@ -18115,39 +18251,41 @@
     </row>
     <row r="48" spans="1:26" ht="27.6">
       <c r="A48" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="G48" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>405</v>
-      </c>
       <c r="I48" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L48" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>893</v>
+      </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -18165,40 +18303,40 @@
     </row>
     <row r="49" spans="1:26" ht="41.4">
       <c r="A49" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="I49" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
@@ -18217,7 +18355,7 @@
     </row>
     <row r="50" spans="1:26" ht="27.6">
       <c r="A50" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>55</v>
@@ -18226,30 +18364,32 @@
         <v>31</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="I50" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L50" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>894</v>
+      </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -18267,7 +18407,7 @@
     </row>
     <row r="51" spans="1:26" ht="41.4">
       <c r="A51" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>55</v>
@@ -18276,31 +18416,31 @@
         <v>50</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="F51" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="I51" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
@@ -18319,7 +18459,7 @@
     </row>
     <row r="52" spans="1:26" ht="41.4">
       <c r="A52" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>55</v>
@@ -18328,31 +18468,31 @@
         <v>31</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="G52" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>427</v>
-      </c>
       <c r="I52" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
@@ -18371,7 +18511,7 @@
     </row>
     <row r="53" spans="1:26" ht="27.6">
       <c r="A53" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>55</v>
@@ -18380,19 +18520,19 @@
         <v>50</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>124</v>
@@ -18401,10 +18541,10 @@
         <v>15</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
@@ -18423,7 +18563,7 @@
     </row>
     <row r="54" spans="1:26" ht="41.4">
       <c r="A54" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>55</v>
@@ -18432,31 +18572,31 @@
         <v>50</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="G54" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>439</v>
-      </c>
       <c r="I54" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
@@ -18475,7 +18615,7 @@
     </row>
     <row r="55" spans="1:26" ht="41.4">
       <c r="A55" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>58</v>
@@ -18484,19 +18624,19 @@
         <v>31</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="G55" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>445</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>124</v>
@@ -18505,9 +18645,11 @@
         <v>15</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L55" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>895</v>
+      </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -18525,7 +18667,7 @@
     </row>
     <row r="56" spans="1:26" ht="41.4">
       <c r="A56" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>58</v>
@@ -18534,19 +18676,19 @@
         <v>31</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="F56" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="G56" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="H56" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>124</v>
@@ -18555,9 +18697,11 @@
         <v>15</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L56" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>896</v>
+      </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -18575,7 +18719,7 @@
     </row>
     <row r="57" spans="1:26" ht="41.4">
       <c r="A57" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>58</v>
@@ -18584,19 +18728,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="G57" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>124</v>
@@ -18605,9 +18749,11 @@
         <v>15</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L57" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>897</v>
+      </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -18625,7 +18771,7 @@
     </row>
     <row r="58" spans="1:26" ht="41.4">
       <c r="A58" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>58</v>
@@ -18634,19 +18780,19 @@
         <v>50</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>124</v>
@@ -18655,9 +18801,11 @@
         <v>15</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L58" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>898</v>
+      </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -18675,7 +18823,7 @@
     </row>
     <row r="59" spans="1:26" ht="27.6">
       <c r="A59" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>58</v>
@@ -18684,19 +18832,19 @@
         <v>50</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="H59" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>124</v>
@@ -18705,10 +18853,10 @@
         <v>15</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
@@ -18727,7 +18875,7 @@
     </row>
     <row r="60" spans="1:26" ht="27.6">
       <c r="A60" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>58</v>
@@ -18736,19 +18884,19 @@
         <v>50</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="G60" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="H60" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>124</v>
@@ -18757,9 +18905,11 @@
         <v>15</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L60" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>899</v>
+      </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
@@ -18777,40 +18927,40 @@
     </row>
     <row r="61" spans="1:26" ht="27.6">
       <c r="A61" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E61" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="G61" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>479</v>
-      </c>
       <c r="I61" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -18829,7 +18979,7 @@
     </row>
     <row r="62" spans="1:26" ht="41.4">
       <c r="A62" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>61</v>
@@ -18838,19 +18988,19 @@
         <v>31</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="G62" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="H62" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>485</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>124</v>
@@ -18859,9 +19009,11 @@
         <v>15</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L62" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>900</v>
+      </c>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
@@ -18879,7 +19031,7 @@
     </row>
     <row r="63" spans="1:26" ht="27.6">
       <c r="A63" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>61</v>
@@ -18888,30 +19040,32 @@
         <v>50</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="G63" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="H63" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="H63" s="3" t="s">
-        <v>491</v>
-      </c>
       <c r="I63" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L63" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>901</v>
+      </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
@@ -18929,7 +19083,7 @@
     </row>
     <row r="64" spans="1:26" ht="27.6">
       <c r="A64" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>61</v>
@@ -18938,19 +19092,19 @@
         <v>50</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="F64" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="G64" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="H64" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>124</v>
@@ -18959,10 +19113,10 @@
         <v>15</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
@@ -18981,7 +19135,7 @@
     </row>
     <row r="65" spans="1:26" ht="27.6">
       <c r="A65" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>61</v>
@@ -18990,19 +19144,19 @@
         <v>50</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="G65" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="H65" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>124</v>
@@ -19011,10 +19165,10 @@
         <v>15</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
@@ -19033,7 +19187,7 @@
     </row>
     <row r="66" spans="1:26" ht="27.6">
       <c r="A66" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>63</v>
@@ -19042,30 +19196,32 @@
         <v>31</v>
       </c>
       <c r="D66" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="G66" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>508</v>
-      </c>
       <c r="I66" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L66" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>902</v>
+      </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
@@ -19083,7 +19239,7 @@
     </row>
     <row r="67" spans="1:26" ht="27.6">
       <c r="A67" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>63</v>
@@ -19092,31 +19248,31 @@
         <v>50</v>
       </c>
       <c r="D67" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="G67" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="H67" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="I67" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
@@ -19135,7 +19291,7 @@
     </row>
     <row r="68" spans="1:26" ht="27.6">
       <c r="A68" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>63</v>
@@ -19144,31 +19300,31 @@
         <v>50</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="G68" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>520</v>
-      </c>
       <c r="I68" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
@@ -19187,7 +19343,7 @@
     </row>
     <row r="69" spans="1:26" ht="27.6">
       <c r="A69" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>63</v>
@@ -19196,19 +19352,19 @@
         <v>50</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="G69" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>526</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>124</v>
@@ -19217,10 +19373,10 @@
         <v>15</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
@@ -19239,28 +19395,28 @@
     </row>
     <row r="70" spans="1:26" ht="27.6">
       <c r="A70" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D70" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="F70" s="3" t="s">
+      <c r="G70" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>124</v>
@@ -19269,10 +19425,10 @@
         <v>15</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
@@ -19291,39 +19447,41 @@
     </row>
     <row r="71" spans="1:26" ht="41.4">
       <c r="A71" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D71" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="G71" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="H71" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>537</v>
-      </c>
       <c r="I71" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L71" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
@@ -19341,39 +19499,41 @@
     </row>
     <row r="72" spans="1:26" ht="27.6">
       <c r="A72" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>543</v>
-      </c>
       <c r="I72" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L72" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>904</v>
+      </c>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
@@ -19391,7 +19551,7 @@
     </row>
     <row r="73" spans="1:26" ht="27.6">
       <c r="A73" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>65</v>
@@ -19400,30 +19560,32 @@
         <v>31</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F73" s="3" t="s">
+      <c r="G73" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="H73" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="H73" s="3" t="s">
-        <v>548</v>
-      </c>
       <c r="I73" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L73" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>905</v>
+      </c>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
@@ -19441,7 +19603,7 @@
     </row>
     <row r="74" spans="1:26" ht="27.6">
       <c r="A74" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>65</v>
@@ -19450,30 +19612,32 @@
         <v>31</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="F74" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="G74" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>554</v>
-      </c>
       <c r="I74" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L74" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>906</v>
+      </c>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
@@ -19491,7 +19655,7 @@
     </row>
     <row r="75" spans="1:26" ht="27.6">
       <c r="A75" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>65</v>
@@ -19500,19 +19664,19 @@
         <v>31</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="F75" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="G75" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="H75" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>124</v>
@@ -19521,9 +19685,11 @@
         <v>15</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L75" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>907</v>
+      </c>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
@@ -19541,7 +19707,7 @@
     </row>
     <row r="76" spans="1:26" ht="41.4">
       <c r="A76" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>65</v>
@@ -19550,31 +19716,31 @@
         <v>50</v>
       </c>
       <c r="D76" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="F76" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="G76" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="H76" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>566</v>
-      </c>
       <c r="I76" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
@@ -19593,7 +19759,7 @@
     </row>
     <row r="77" spans="1:26" ht="41.4">
       <c r="A77" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>65</v>
@@ -19602,19 +19768,19 @@
         <v>50</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="F77" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="G77" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="H77" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>124</v>
@@ -19623,10 +19789,10 @@
         <v>15</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
@@ -19645,28 +19811,28 @@
     </row>
     <row r="78" spans="1:26" ht="27.6">
       <c r="A78" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D78" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="G78" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="H78" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>578</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>124</v>
@@ -19675,9 +19841,11 @@
         <v>15</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L78" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>908</v>
+      </c>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
@@ -19695,7 +19863,7 @@
     </row>
     <row r="79" spans="1:26" ht="27.6">
       <c r="A79" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>67</v>
@@ -19704,19 +19872,19 @@
         <v>31</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="F79" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="G79" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="H79" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>124</v>
@@ -19725,9 +19893,11 @@
         <v>15</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L79" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>909</v>
+      </c>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
@@ -19745,7 +19915,7 @@
     </row>
     <row r="80" spans="1:26" ht="27.6">
       <c r="A80" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>67</v>
@@ -19754,19 +19924,19 @@
         <v>31</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="F80" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="G80" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="H80" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>590</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>124</v>
@@ -19775,9 +19945,11 @@
         <v>15</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L80" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>910</v>
+      </c>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
@@ -19795,40 +19967,40 @@
     </row>
     <row r="81" spans="1:26" ht="27.6">
       <c r="A81" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E81" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="G81" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="H81" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>595</v>
-      </c>
       <c r="I81" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
@@ -19847,7 +20019,7 @@
     </row>
     <row r="82" spans="1:26" ht="27.6">
       <c r="A82" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>67</v>
@@ -19856,19 +20028,19 @@
         <v>31</v>
       </c>
       <c r="D82" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="F82" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="F82" s="3" t="s">
+      <c r="G82" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="H82" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>124</v>
@@ -19877,9 +20049,11 @@
         <v>15</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L82" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>911</v>
+      </c>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
@@ -19897,7 +20071,7 @@
     </row>
     <row r="83" spans="1:26" ht="27.6">
       <c r="A83" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>67</v>
@@ -19906,19 +20080,19 @@
         <v>31</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="G83" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>124</v>
@@ -19927,9 +20101,11 @@
         <v>15</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L83" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>912</v>
+      </c>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
@@ -19947,7 +20123,7 @@
     </row>
     <row r="84" spans="1:26" ht="27.6">
       <c r="A84" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>67</v>
@@ -19956,19 +20132,19 @@
         <v>50</v>
       </c>
       <c r="D84" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="F84" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="G84" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="H84" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>612</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>124</v>
@@ -19977,9 +20153,11 @@
         <v>15</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L84" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>913</v>
+      </c>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
@@ -19997,7 +20175,7 @@
     </row>
     <row r="85" spans="1:26" ht="41.4">
       <c r="A85" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>69</v>
@@ -20006,31 +20184,31 @@
         <v>31</v>
       </c>
       <c r="D85" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="F85" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="G85" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="H85" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="H85" s="3" t="s">
-        <v>618</v>
-      </c>
       <c r="I85" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
@@ -20049,7 +20227,7 @@
     </row>
     <row r="86" spans="1:26" ht="41.4">
       <c r="A86" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>69</v>
@@ -20058,31 +20236,31 @@
         <v>31</v>
       </c>
       <c r="D86" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="F86" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="G86" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="H86" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="H86" s="3" t="s">
-        <v>624</v>
-      </c>
       <c r="I86" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K86" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="L86" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>817</v>
       </c>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
@@ -20101,7 +20279,7 @@
     </row>
     <row r="87" spans="1:26" ht="41.4">
       <c r="A87" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>69</v>
@@ -20110,31 +20288,31 @@
         <v>50</v>
       </c>
       <c r="D87" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="F87" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="G87" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="H87" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="H87" s="3" t="s">
-        <v>630</v>
-      </c>
       <c r="I87" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
@@ -20153,7 +20331,7 @@
     </row>
     <row r="88" spans="1:26" ht="27.6">
       <c r="A88" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>69</v>
@@ -20162,19 +20340,19 @@
         <v>50</v>
       </c>
       <c r="D88" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="F88" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="G88" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="H88" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>636</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>124</v>
@@ -20183,10 +20361,10 @@
         <v>15</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
@@ -20205,7 +20383,7 @@
     </row>
     <row r="89" spans="1:26" ht="41.4">
       <c r="A89" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>69</v>
@@ -20214,19 +20392,19 @@
         <v>50</v>
       </c>
       <c r="D89" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="G89" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>124</v>
@@ -20235,10 +20413,10 @@
         <v>15</v>
       </c>
       <c r="K89" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
@@ -20257,40 +20435,40 @@
     </row>
     <row r="90" spans="1:26" ht="41.4">
       <c r="A90" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D90" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="F90" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="G90" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="H90" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>648</v>
-      </c>
       <c r="I90" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
@@ -20309,7 +20487,7 @@
     </row>
     <row r="91" spans="1:26" ht="41.4">
       <c r="A91" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>72</v>
@@ -20318,19 +20496,19 @@
         <v>31</v>
       </c>
       <c r="D91" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="F91" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="G91" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>124</v>
@@ -20339,9 +20517,11 @@
         <v>15</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L91" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>914</v>
+      </c>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
@@ -20359,7 +20539,7 @@
     </row>
     <row r="92" spans="1:26" ht="27.6">
       <c r="A92" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>72</v>
@@ -20368,30 +20548,32 @@
         <v>31</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E92" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="F92" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="G92" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="H92" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>659</v>
-      </c>
       <c r="I92" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L92" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>915</v>
+      </c>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
@@ -20409,7 +20591,7 @@
     </row>
     <row r="93" spans="1:26" ht="41.4">
       <c r="A93" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>72</v>
@@ -20418,19 +20600,19 @@
         <v>31</v>
       </c>
       <c r="D93" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="F93" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="G93" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="H93" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>665</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>124</v>
@@ -20439,9 +20621,11 @@
         <v>15</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L93" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>916</v>
+      </c>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
@@ -20459,7 +20643,7 @@
     </row>
     <row r="94" spans="1:26" ht="27.6">
       <c r="A94" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>72</v>
@@ -20468,30 +20652,32 @@
         <v>50</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F94" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G94" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="I94" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>671</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L94" s="1"/>
+        <v>832</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>917</v>
+      </c>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
@@ -20509,40 +20695,40 @@
     </row>
     <row r="95" spans="1:26" ht="27.6">
       <c r="A95" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D95" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="F95" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="G95" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="H95" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>677</v>
-      </c>
       <c r="I95" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
@@ -20561,7 +20747,7 @@
     </row>
     <row r="96" spans="1:26" ht="41.4">
       <c r="A96" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>74</v>
@@ -20570,31 +20756,31 @@
         <v>31</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>683</v>
-      </c>
       <c r="I96" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
@@ -20613,7 +20799,7 @@
     </row>
     <row r="97" spans="1:26" ht="27.6">
       <c r="A97" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>74</v>
@@ -20622,31 +20808,31 @@
         <v>31</v>
       </c>
       <c r="D97" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="F97" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="G97" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="H97" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>689</v>
-      </c>
       <c r="I97" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J97" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
@@ -20665,7 +20851,7 @@
     </row>
     <row r="98" spans="1:26" ht="41.4">
       <c r="A98" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>74</v>
@@ -20674,31 +20860,31 @@
         <v>31</v>
       </c>
       <c r="D98" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="F98" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="G98" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="H98" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="H98" s="3" t="s">
-        <v>695</v>
-      </c>
       <c r="I98" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J98" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
@@ -20717,7 +20903,7 @@
     </row>
     <row r="99" spans="1:26" ht="27.6">
       <c r="A99" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>74</v>
@@ -20726,31 +20912,31 @@
         <v>31</v>
       </c>
       <c r="D99" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="F99" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="G99" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="H99" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="H99" s="3" t="s">
-        <v>701</v>
-      </c>
       <c r="I99" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
@@ -20769,7 +20955,7 @@
     </row>
     <row r="100" spans="1:26" ht="41.4">
       <c r="A100" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>74</v>
@@ -20778,31 +20964,31 @@
         <v>31</v>
       </c>
       <c r="D100" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="G100" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="H100" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>707</v>
-      </c>
       <c r="I100" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
@@ -20821,7 +21007,7 @@
     </row>
     <row r="101" spans="1:26" ht="41.4">
       <c r="A101" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>74</v>
@@ -20830,30 +21016,32 @@
         <v>50</v>
       </c>
       <c r="D101" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="F101" s="3" t="s">
+      <c r="G101" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>712</v>
-      </c>
       <c r="I101" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L101" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>918</v>
+      </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
@@ -20871,40 +21059,40 @@
     </row>
     <row r="102" spans="1:26" ht="41.4">
       <c r="A102" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D102" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="E102" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="F102" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="G102" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="H102" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>718</v>
-      </c>
       <c r="I102" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
@@ -20923,7 +21111,7 @@
     </row>
     <row r="103" spans="1:26" ht="27.6">
       <c r="A103" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>76</v>
@@ -20932,19 +21120,19 @@
         <v>31</v>
       </c>
       <c r="D103" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="F103" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="G103" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="H103" s="3" t="s">
         <v>723</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>724</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>124</v>
@@ -20953,10 +21141,10 @@
         <v>15</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
@@ -20975,7 +21163,7 @@
     </row>
     <row r="104" spans="1:26" ht="27.6">
       <c r="A104" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>76</v>
@@ -20984,31 +21172,31 @@
         <v>31</v>
       </c>
       <c r="D104" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="F104" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="G104" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="H104" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="H104" s="3" t="s">
-        <v>730</v>
-      </c>
       <c r="I104" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
@@ -21027,7 +21215,7 @@
     </row>
     <row r="105" spans="1:26" ht="27.6">
       <c r="A105" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>76</v>
@@ -21036,31 +21224,31 @@
         <v>31</v>
       </c>
       <c r="D105" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="G105" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="H105" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="H105" s="3" t="s">
-        <v>736</v>
-      </c>
       <c r="I105" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J105" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -21079,7 +21267,7 @@
     </row>
     <row r="106" spans="1:26" ht="27.6">
       <c r="A106" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>76</v>
@@ -21088,31 +21276,31 @@
         <v>31</v>
       </c>
       <c r="D106" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="F106" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="F106" s="3" t="s">
+      <c r="G106" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="H106" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="H106" s="3" t="s">
-        <v>741</v>
-      </c>
       <c r="I106" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J106" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
@@ -21131,7 +21319,7 @@
     </row>
     <row r="107" spans="1:26" ht="41.4">
       <c r="A107" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>76</v>
@@ -21140,30 +21328,32 @@
         <v>50</v>
       </c>
       <c r="D107" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="F107" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="G107" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="H107" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="H107" s="3" t="s">
-        <v>747</v>
-      </c>
       <c r="I107" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J107" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L107" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>919</v>
+      </c>
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
@@ -21181,7 +21371,7 @@
     </row>
     <row r="108" spans="1:26" ht="41.4">
       <c r="A108" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>76</v>
@@ -21190,30 +21380,32 @@
         <v>50</v>
       </c>
       <c r="D108" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="E108" s="3" t="s">
+      <c r="F108" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="G108" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="H108" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="H108" s="3" t="s">
-        <v>753</v>
-      </c>
       <c r="I108" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L108" s="1"/>
+        <v>832</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>920</v>
+      </c>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
@@ -23807,13 +23999,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C108">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>C2="Critical"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>C2="High"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>C2="Medium"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23847,7 +24039,7 @@
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="5" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -23933,22 +24125,22 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -23974,7 +24166,7 @@
         <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -23986,7 +24178,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -24012,7 +24204,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -24021,10 +24213,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>762</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>763</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -24050,7 +24242,7 @@
         <v>83</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -24062,7 +24254,7 @@
         <v>13</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -24085,10 +24277,10 @@
     </row>
     <row r="8" spans="1:26" ht="27.6">
       <c r="A8" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>766</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>767</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -24100,7 +24292,7 @@
         <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -24126,19 +24318,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>772</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -24161,10 +24353,10 @@
     </row>
     <row r="10" spans="1:26" ht="27.6">
       <c r="A10" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>773</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>774</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -24249,16 +24441,16 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -24285,16 +24477,16 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>781</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>782</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -24321,16 +24513,16 @@
     </row>
     <row r="15" spans="1:26" ht="27.6">
       <c r="A15" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>785</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>786</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -24360,13 +24552,13 @@
         <v>43</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>788</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>789</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -24396,13 +24588,13 @@
         <v>45</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>792</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -24432,13 +24624,13 @@
         <v>47</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>794</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>795</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -24465,16 +24657,16 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>798</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -24501,16 +24693,16 @@
     </row>
     <row r="20" spans="1:26" ht="27.6">
       <c r="A20" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -24537,16 +24729,16 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>805</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -24573,16 +24765,16 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>809</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>810</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -24609,16 +24801,16 @@
     </row>
     <row r="23" spans="1:26" ht="27.6">
       <c r="A23" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>813</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>814</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
